--- a/rates.xlsx
+++ b/rates.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="176">
   <si>
     <t>Дата</t>
   </si>
@@ -35,7 +35,439 @@
     <t>Курс за 1 единицу валюты</t>
   </si>
   <si>
-    <t>31.05.2026 22:23:46</t>
+    <t>Дата сохраненного курса</t>
+  </si>
+  <si>
+    <t>Сохраненный курс</t>
+  </si>
+  <si>
+    <t>Изменение курса</t>
+  </si>
+  <si>
+    <t>21.06.2026 14:17:03</t>
+  </si>
+  <si>
+    <t>036</t>
+  </si>
+  <si>
+    <t>AUD</t>
+  </si>
+  <si>
+    <t>Австралийский доллар</t>
+  </si>
+  <si>
+    <t>21.06.2026 13:33:33</t>
+  </si>
+  <si>
+    <t>Изменение курса с 21.06.2026 13:33:33: курс вырос на 1,0000 руб.</t>
+  </si>
+  <si>
+    <t>944</t>
+  </si>
+  <si>
+    <t>AZN</t>
+  </si>
+  <si>
+    <t>Азербайджанский манат</t>
+  </si>
+  <si>
+    <t>Изменение курса с 21.06.2026 13:33:33: курс не изменился.</t>
+  </si>
+  <si>
+    <t>012</t>
+  </si>
+  <si>
+    <t>DZD</t>
+  </si>
+  <si>
+    <t>Алжирских динаров</t>
+  </si>
+  <si>
+    <t>826</t>
+  </si>
+  <si>
+    <t>GBP</t>
+  </si>
+  <si>
+    <t>Фунт стерлингов</t>
+  </si>
+  <si>
+    <t>051</t>
+  </si>
+  <si>
+    <t>AMD</t>
+  </si>
+  <si>
+    <t>Армянских драмов</t>
+  </si>
+  <si>
+    <t>048</t>
+  </si>
+  <si>
+    <t>BHD</t>
+  </si>
+  <si>
+    <t>Бахрейнский динар</t>
+  </si>
+  <si>
+    <t>933</t>
+  </si>
+  <si>
+    <t>BYN</t>
+  </si>
+  <si>
+    <t>Белорусский рубль</t>
+  </si>
+  <si>
+    <t>068</t>
+  </si>
+  <si>
+    <t>BOB</t>
+  </si>
+  <si>
+    <t>Боливиано</t>
+  </si>
+  <si>
+    <t>986</t>
+  </si>
+  <si>
+    <t>BRL</t>
+  </si>
+  <si>
+    <t>Бразильский реал</t>
+  </si>
+  <si>
+    <t>348</t>
+  </si>
+  <si>
+    <t>HUF</t>
+  </si>
+  <si>
+    <t>Форинтов</t>
+  </si>
+  <si>
+    <t>704</t>
+  </si>
+  <si>
+    <t>VND</t>
+  </si>
+  <si>
+    <t>Донгов</t>
+  </si>
+  <si>
+    <t>344</t>
+  </si>
+  <si>
+    <t>HKD</t>
+  </si>
+  <si>
+    <t>Гонконгских долларов</t>
+  </si>
+  <si>
+    <t>981</t>
+  </si>
+  <si>
+    <t>GEL</t>
+  </si>
+  <si>
+    <t>Лари</t>
+  </si>
+  <si>
+    <t>208</t>
+  </si>
+  <si>
+    <t>DKK</t>
+  </si>
+  <si>
+    <t>Датская крона</t>
+  </si>
+  <si>
+    <t>784</t>
+  </si>
+  <si>
+    <t>AED</t>
+  </si>
+  <si>
+    <t>Дирхам ОАЭ</t>
+  </si>
+  <si>
+    <t>840</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>Доллар США</t>
+  </si>
+  <si>
+    <t>978</t>
+  </si>
+  <si>
+    <t>EUR</t>
+  </si>
+  <si>
+    <t>Евро</t>
+  </si>
+  <si>
+    <t>818</t>
+  </si>
+  <si>
+    <t>EGP</t>
+  </si>
+  <si>
+    <t>Египетских фунтов</t>
+  </si>
+  <si>
+    <t>356</t>
+  </si>
+  <si>
+    <t>INR</t>
+  </si>
+  <si>
+    <t>Индийских рупий</t>
+  </si>
+  <si>
+    <t>360</t>
+  </si>
+  <si>
+    <t>IDR</t>
+  </si>
+  <si>
+    <t>Рупий</t>
+  </si>
+  <si>
+    <t>364</t>
+  </si>
+  <si>
+    <t>IRR</t>
+  </si>
+  <si>
+    <t>Иранских риалов</t>
+  </si>
+  <si>
+    <t>398</t>
+  </si>
+  <si>
+    <t>KZT</t>
+  </si>
+  <si>
+    <t>Тенге</t>
+  </si>
+  <si>
+    <t>124</t>
+  </si>
+  <si>
+    <t>CAD</t>
+  </si>
+  <si>
+    <t>Канадский доллар</t>
+  </si>
+  <si>
+    <t>634</t>
+  </si>
+  <si>
+    <t>QAR</t>
+  </si>
+  <si>
+    <t>Катарский риал</t>
+  </si>
+  <si>
+    <t>417</t>
+  </si>
+  <si>
+    <t>KGS</t>
+  </si>
+  <si>
+    <t>Сомов</t>
+  </si>
+  <si>
+    <t>156</t>
+  </si>
+  <si>
+    <t>CNY</t>
+  </si>
+  <si>
+    <t>Юань</t>
+  </si>
+  <si>
+    <t>192</t>
+  </si>
+  <si>
+    <t>CUP</t>
+  </si>
+  <si>
+    <t>Кубинских песо</t>
+  </si>
+  <si>
+    <t>498</t>
+  </si>
+  <si>
+    <t>MDL</t>
+  </si>
+  <si>
+    <t>Молдавских леев</t>
+  </si>
+  <si>
+    <t>496</t>
+  </si>
+  <si>
+    <t>MNT</t>
+  </si>
+  <si>
+    <t>Тугриков</t>
+  </si>
+  <si>
+    <t>566</t>
+  </si>
+  <si>
+    <t>NGN</t>
+  </si>
+  <si>
+    <t>Найр</t>
+  </si>
+  <si>
+    <t>554</t>
+  </si>
+  <si>
+    <t>NZD</t>
+  </si>
+  <si>
+    <t>Новозеландский доллар</t>
+  </si>
+  <si>
+    <t>578</t>
+  </si>
+  <si>
+    <t>NOK</t>
+  </si>
+  <si>
+    <t>Норвежских крон</t>
+  </si>
+  <si>
+    <t>512</t>
+  </si>
+  <si>
+    <t>OMR</t>
+  </si>
+  <si>
+    <t>Оманский риал</t>
+  </si>
+  <si>
+    <t>985</t>
+  </si>
+  <si>
+    <t>PLN</t>
+  </si>
+  <si>
+    <t>Злотый</t>
+  </si>
+  <si>
+    <t>682</t>
+  </si>
+  <si>
+    <t>SAR</t>
+  </si>
+  <si>
+    <t>Саудовский риял</t>
+  </si>
+  <si>
+    <t>946</t>
+  </si>
+  <si>
+    <t>RON</t>
+  </si>
+  <si>
+    <t>Румынский лей</t>
+  </si>
+  <si>
+    <t>960</t>
+  </si>
+  <si>
+    <t>XDR</t>
+  </si>
+  <si>
+    <t>СДР (специальные права заимствования)</t>
+  </si>
+  <si>
+    <t>702</t>
+  </si>
+  <si>
+    <t>SGD</t>
+  </si>
+  <si>
+    <t>Сингапурский доллар</t>
+  </si>
+  <si>
+    <t>972</t>
+  </si>
+  <si>
+    <t>TJS</t>
+  </si>
+  <si>
+    <t>Сомони</t>
+  </si>
+  <si>
+    <t>764</t>
+  </si>
+  <si>
+    <t>THB</t>
+  </si>
+  <si>
+    <t>Батов</t>
+  </si>
+  <si>
+    <t>050</t>
+  </si>
+  <si>
+    <t>BDT</t>
+  </si>
+  <si>
+    <t>Так</t>
+  </si>
+  <si>
+    <t>949</t>
+  </si>
+  <si>
+    <t>TRY</t>
+  </si>
+  <si>
+    <t>Турецких лир</t>
+  </si>
+  <si>
+    <t>934</t>
+  </si>
+  <si>
+    <t>TMT</t>
+  </si>
+  <si>
+    <t>Новый туркменский манат</t>
+  </si>
+  <si>
+    <t>860</t>
+  </si>
+  <si>
+    <t>UZS</t>
+  </si>
+  <si>
+    <t>Узбекских сумов</t>
+  </si>
+  <si>
+    <t>980</t>
+  </si>
+  <si>
+    <t>UAH</t>
+  </si>
+  <si>
+    <t>Гривен</t>
+  </si>
+  <si>
+    <t>203</t>
+  </si>
+  <si>
+    <t>CZK</t>
+  </si>
+  <si>
+    <t>Чешских крон</t>
   </si>
   <si>
     <t>752</t>
@@ -45,6 +477,69 @@
   </si>
   <si>
     <t>Шведских крон</t>
+  </si>
+  <si>
+    <t>756</t>
+  </si>
+  <si>
+    <t>CHF</t>
+  </si>
+  <si>
+    <t>Швейцарский франк</t>
+  </si>
+  <si>
+    <t>230</t>
+  </si>
+  <si>
+    <t>ETB</t>
+  </si>
+  <si>
+    <t>Эфиопских быров</t>
+  </si>
+  <si>
+    <t>941</t>
+  </si>
+  <si>
+    <t>RSD</t>
+  </si>
+  <si>
+    <t>Сербских динаров</t>
+  </si>
+  <si>
+    <t>710</t>
+  </si>
+  <si>
+    <t>ZAR</t>
+  </si>
+  <si>
+    <t>Рэндов</t>
+  </si>
+  <si>
+    <t>410</t>
+  </si>
+  <si>
+    <t>KRW</t>
+  </si>
+  <si>
+    <t>Вон</t>
+  </si>
+  <si>
+    <t>392</t>
+  </si>
+  <si>
+    <t>JPY</t>
+  </si>
+  <si>
+    <t>Иен</t>
+  </si>
+  <si>
+    <t>104</t>
+  </si>
+  <si>
+    <t>MMK</t>
+  </si>
+  <si>
+    <t>Кьятов</t>
   </si>
 </sst>
 </file>
@@ -89,16 +584,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:J55"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="19.43359375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="14.62890625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="15.296875" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="15.42578125" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="39.72265625" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="9.59765625" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="16.66015625" customWidth="true" bestFit="true"/>
     <col min="7" max="7" width="25.6015625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="24.5234375" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="18.41015625" customWidth="true" bestFit="true"/>
+    <col min="10" max="10" width="62.84375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -123,74 +621,1742 @@
       <c r="G1" t="s" s="0">
         <v>6</v>
       </c>
+      <c r="H1" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s" s="0">
+        <v>9</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E2" t="n" s="0">
-        <v>10.0</v>
+        <v>1.0</v>
       </c>
       <c r="F2" t="n" s="0">
-        <v>76.2433</v>
+        <v>51.444</v>
       </c>
       <c r="G2" t="n" s="0">
-        <v>7.6243300000000005</v>
+        <v>51.444</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="I2" t="n" s="0">
+        <v>50.444</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>15</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E3" t="n" s="0">
-        <v>10.0</v>
+        <v>1.0</v>
       </c>
       <c r="F3" t="n" s="0">
-        <v>76.2433</v>
+        <v>43.1994</v>
       </c>
       <c r="G3" t="n" s="0">
-        <v>7.6243300000000005</v>
+        <v>43.1994</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="I3" t="n" s="0">
+        <v>43.1994</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>19</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E4" t="n" s="0">
+        <v>100.0</v>
+      </c>
+      <c r="F4" t="n" s="0">
+        <v>55.0958</v>
+      </c>
+      <c r="G4" t="n" s="0">
+        <v>0.550958</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="I4" t="n" s="0">
+        <v>0.550958</v>
+      </c>
+      <c r="J4" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="E5" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F5" t="n" s="0">
+        <v>97.3287</v>
+      </c>
+      <c r="G5" t="n" s="0">
+        <v>97.3287</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="I5" t="n" s="0">
+        <v>97.3287</v>
+      </c>
+      <c r="J5" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="C6" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="E6" t="n" s="0">
+        <v>100.0</v>
+      </c>
+      <c r="F6" t="n" s="0">
+        <v>19.9481</v>
+      </c>
+      <c r="G6" t="n" s="0">
+        <v>0.199481</v>
+      </c>
+      <c r="H6" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="I6" t="n" s="0">
+        <v>0.199481</v>
+      </c>
+      <c r="J6" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="C7" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="E7" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F7" t="n" s="0">
+        <v>195.2743</v>
+      </c>
+      <c r="G7" t="n" s="0">
+        <v>195.2743</v>
+      </c>
+      <c r="H7" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="I7" t="n" s="0">
+        <v>195.2743</v>
+      </c>
+      <c r="J7" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="C8" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="E8" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F8" t="n" s="0">
+        <v>26.3298</v>
+      </c>
+      <c r="G8" t="n" s="0">
+        <v>26.3298</v>
+      </c>
+      <c r="H8" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="I8" t="n" s="0">
+        <v>26.3298</v>
+      </c>
+      <c r="J8" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="C9" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="D9" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="E9" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F9" t="n" s="0">
+        <v>10.6279</v>
+      </c>
+      <c r="G9" t="n" s="0">
+        <v>10.6279</v>
+      </c>
+      <c r="H9" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="I9" t="n" s="0">
+        <v>10.6279</v>
+      </c>
+      <c r="J9" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C10" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="D10" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="E10" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F10" t="n" s="0">
+        <v>14.2296</v>
+      </c>
+      <c r="G10" t="n" s="0">
+        <v>14.2296</v>
+      </c>
+      <c r="H10" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="I10" t="n" s="0">
+        <v>14.2296</v>
+      </c>
+      <c r="J10" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C11" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="D11" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="E11" t="n" s="0">
+        <v>100.0</v>
+      </c>
+      <c r="F11" t="n" s="0">
+        <v>23.8593</v>
+      </c>
+      <c r="G11" t="n" s="0">
+        <v>0.238593</v>
+      </c>
+      <c r="H11" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="I11" t="n" s="0">
+        <v>0.238593</v>
+      </c>
+      <c r="J11" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="C12" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="D12" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="E12" t="n" s="0">
+        <v>10000.0</v>
+      </c>
+      <c r="F12" t="n" s="0">
+        <v>29.1644</v>
+      </c>
+      <c r="G12" t="n" s="0">
+        <v>0.00291644</v>
+      </c>
+      <c r="H12" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="I12" t="n" s="0">
+        <v>0.00291644</v>
+      </c>
+      <c r="J12" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="C13" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="D13" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="E13" t="n" s="0">
         <v>10.0</v>
       </c>
-      <c r="F4" t="n" s="0">
-        <v>76.2433</v>
-      </c>
-      <c r="G4" t="n" s="0">
-        <v>7.6243300000000005</v>
+      <c r="F13" t="n" s="0">
+        <v>93.6722</v>
+      </c>
+      <c r="G13" t="n" s="0">
+        <v>9.36722</v>
+      </c>
+      <c r="H13" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="I13" t="n" s="0">
+        <v>9.36722</v>
+      </c>
+      <c r="J13" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="C14" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="D14" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="E14" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F14" t="n" s="0">
+        <v>27.6846</v>
+      </c>
+      <c r="G14" t="n" s="0">
+        <v>27.6846</v>
+      </c>
+      <c r="H14" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="I14" t="n" s="0">
+        <v>27.6846</v>
+      </c>
+      <c r="J14" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B15" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="C15" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="D15" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="E15" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F15" t="n" s="0">
+        <v>11.2604</v>
+      </c>
+      <c r="G15" t="n" s="0">
+        <v>11.2604</v>
+      </c>
+      <c r="H15" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="I15" t="n" s="0">
+        <v>11.2604</v>
+      </c>
+      <c r="J15" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B16" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="C16" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="D16" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="E16" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F16" t="n" s="0">
+        <v>19.997</v>
+      </c>
+      <c r="G16" t="n" s="0">
+        <v>19.997</v>
+      </c>
+      <c r="H16" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="I16" t="n" s="0">
+        <v>19.997</v>
+      </c>
+      <c r="J16" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B17" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="C17" t="s" s="0">
+        <v>60</v>
+      </c>
+      <c r="D17" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="E17" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F17" t="n" s="0">
+        <v>73.439</v>
+      </c>
+      <c r="G17" t="n" s="0">
+        <v>73.439</v>
+      </c>
+      <c r="H17" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="I17" t="n" s="0">
+        <v>73.439</v>
+      </c>
+      <c r="J17" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B18" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="C18" t="s" s="0">
+        <v>63</v>
+      </c>
+      <c r="D18" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="E18" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F18" t="n" s="0">
+        <v>84.1684</v>
+      </c>
+      <c r="G18" t="n" s="0">
+        <v>84.1684</v>
+      </c>
+      <c r="H18" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="I18" t="n" s="0">
+        <v>84.1684</v>
+      </c>
+      <c r="J18" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B19" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="C19" t="s" s="0">
+        <v>66</v>
+      </c>
+      <c r="D19" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="E19" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="F19" t="n" s="0">
+        <v>14.712</v>
+      </c>
+      <c r="G19" t="n" s="0">
+        <v>1.4712</v>
+      </c>
+      <c r="H19" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="I19" t="n" s="0">
+        <v>1.4712</v>
+      </c>
+      <c r="J19" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B20" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="C20" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D20" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="E20" t="n" s="0">
+        <v>100.0</v>
+      </c>
+      <c r="F20" t="n" s="0">
+        <v>77.735</v>
+      </c>
+      <c r="G20" t="n" s="0">
+        <v>0.77735</v>
+      </c>
+      <c r="H20" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="I20" t="n" s="0">
+        <v>0.77735</v>
+      </c>
+      <c r="J20" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B21" t="s" s="0">
+        <v>71</v>
+      </c>
+      <c r="C21" t="s" s="0">
+        <v>72</v>
+      </c>
+      <c r="D21" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="E21" t="n" s="0">
+        <v>10000.0</v>
+      </c>
+      <c r="F21" t="n" s="0">
+        <v>41.1977</v>
+      </c>
+      <c r="G21" t="n" s="0">
+        <v>0.00411977</v>
+      </c>
+      <c r="H21" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="I21" t="n" s="0">
+        <v>0.00411977</v>
+      </c>
+      <c r="J21" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B22" t="s" s="0">
+        <v>74</v>
+      </c>
+      <c r="C22" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="D22" t="s" s="0">
+        <v>76</v>
+      </c>
+      <c r="E22" t="n" s="0">
+        <v>1000000.0</v>
+      </c>
+      <c r="F22" t="n" s="0">
+        <v>50.6686</v>
+      </c>
+      <c r="G22" t="n" s="0">
+        <v>5.06686E-5</v>
+      </c>
+      <c r="H22" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="I22" t="n" s="0">
+        <v>5.06686E-5</v>
+      </c>
+      <c r="J22" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B23" t="s" s="0">
+        <v>77</v>
+      </c>
+      <c r="C23" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="D23" t="s" s="0">
+        <v>79</v>
+      </c>
+      <c r="E23" t="n" s="0">
+        <v>100.0</v>
+      </c>
+      <c r="F23" t="n" s="0">
+        <v>15.0573</v>
+      </c>
+      <c r="G23" t="n" s="0">
+        <v>0.15057299999999998</v>
+      </c>
+      <c r="H23" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="I23" t="n" s="0">
+        <v>0.15057299999999998</v>
+      </c>
+      <c r="J23" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B24" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="C24" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="D24" t="s" s="0">
+        <v>82</v>
+      </c>
+      <c r="E24" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F24" t="n" s="0">
+        <v>51.9701</v>
+      </c>
+      <c r="G24" t="n" s="0">
+        <v>51.9701</v>
+      </c>
+      <c r="H24" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="I24" t="n" s="0">
+        <v>51.9701</v>
+      </c>
+      <c r="J24" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B25" t="s" s="0">
+        <v>83</v>
+      </c>
+      <c r="C25" t="s" s="0">
+        <v>84</v>
+      </c>
+      <c r="D25" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="E25" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F25" t="n" s="0">
+        <v>20.1755</v>
+      </c>
+      <c r="G25" t="n" s="0">
+        <v>20.1755</v>
+      </c>
+      <c r="H25" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="I25" t="n" s="0">
+        <v>20.1755</v>
+      </c>
+      <c r="J25" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B26" t="s" s="0">
+        <v>86</v>
+      </c>
+      <c r="C26" t="s" s="0">
+        <v>87</v>
+      </c>
+      <c r="D26" t="s" s="0">
+        <v>88</v>
+      </c>
+      <c r="E26" t="n" s="0">
+        <v>100.0</v>
+      </c>
+      <c r="F26" t="n" s="0">
+        <v>83.9783</v>
+      </c>
+      <c r="G26" t="n" s="0">
+        <v>0.8397830000000001</v>
+      </c>
+      <c r="H26" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="I26" t="n" s="0">
+        <v>0.8397830000000001</v>
+      </c>
+      <c r="J26" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B27" t="s" s="0">
+        <v>89</v>
+      </c>
+      <c r="C27" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="D27" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="E27" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F27" t="n" s="0">
+        <v>10.806</v>
+      </c>
+      <c r="G27" t="n" s="0">
+        <v>10.806</v>
+      </c>
+      <c r="H27" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="I27" t="n" s="0">
+        <v>10.806</v>
+      </c>
+      <c r="J27" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B28" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C28" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="D28" t="s" s="0">
+        <v>94</v>
+      </c>
+      <c r="E28" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="F28" t="n" s="0">
+        <v>30.5996</v>
+      </c>
+      <c r="G28" t="n" s="0">
+        <v>3.05996</v>
+      </c>
+      <c r="H28" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="I28" t="n" s="0">
+        <v>3.05996</v>
+      </c>
+      <c r="J28" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B29" t="s" s="0">
+        <v>95</v>
+      </c>
+      <c r="C29" t="s" s="0">
+        <v>96</v>
+      </c>
+      <c r="D29" t="s" s="0">
+        <v>97</v>
+      </c>
+      <c r="E29" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="F29" t="n" s="0">
+        <v>41.6382</v>
+      </c>
+      <c r="G29" t="n" s="0">
+        <v>4.163819999999999</v>
+      </c>
+      <c r="H29" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="I29" t="n" s="0">
+        <v>4.163819999999999</v>
+      </c>
+      <c r="J29" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B30" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="C30" t="s" s="0">
+        <v>99</v>
+      </c>
+      <c r="D30" t="s" s="0">
+        <v>100</v>
+      </c>
+      <c r="E30" t="n" s="0">
+        <v>1000.0</v>
+      </c>
+      <c r="F30" t="n" s="0">
+        <v>20.5346</v>
+      </c>
+      <c r="G30" t="n" s="0">
+        <v>0.0205346</v>
+      </c>
+      <c r="H30" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="I30" t="n" s="0">
+        <v>0.0205346</v>
+      </c>
+      <c r="J30" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B31" t="s" s="0">
+        <v>101</v>
+      </c>
+      <c r="C31" t="s" s="0">
+        <v>102</v>
+      </c>
+      <c r="D31" t="s" s="0">
+        <v>103</v>
+      </c>
+      <c r="E31" t="n" s="0">
+        <v>1000.0</v>
+      </c>
+      <c r="F31" t="n" s="0">
+        <v>53.8684</v>
+      </c>
+      <c r="G31" t="n" s="0">
+        <v>0.053868400000000004</v>
+      </c>
+      <c r="H31" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="I31" t="n" s="0">
+        <v>0.053868400000000004</v>
+      </c>
+      <c r="J31" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B32" t="s" s="0">
+        <v>104</v>
+      </c>
+      <c r="C32" t="s" s="0">
+        <v>105</v>
+      </c>
+      <c r="D32" t="s" s="0">
+        <v>106</v>
+      </c>
+      <c r="E32" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F32" t="n" s="0">
+        <v>42.2054</v>
+      </c>
+      <c r="G32" t="n" s="0">
+        <v>42.2054</v>
+      </c>
+      <c r="H32" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="I32" t="n" s="0">
+        <v>42.2054</v>
+      </c>
+      <c r="J32" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B33" t="s" s="0">
+        <v>107</v>
+      </c>
+      <c r="C33" t="s" s="0">
+        <v>108</v>
+      </c>
+      <c r="D33" t="s" s="0">
+        <v>109</v>
+      </c>
+      <c r="E33" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="F33" t="n" s="0">
+        <v>75.7931</v>
+      </c>
+      <c r="G33" t="n" s="0">
+        <v>7.5793099999999995</v>
+      </c>
+      <c r="H33" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="I33" t="n" s="0">
+        <v>7.5793099999999995</v>
+      </c>
+      <c r="J33" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B34" t="s" s="0">
+        <v>110</v>
+      </c>
+      <c r="C34" t="s" s="0">
+        <v>111</v>
+      </c>
+      <c r="D34" t="s" s="0">
+        <v>112</v>
+      </c>
+      <c r="E34" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F34" t="n" s="0">
+        <v>190.9987</v>
+      </c>
+      <c r="G34" t="n" s="0">
+        <v>190.9987</v>
+      </c>
+      <c r="H34" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="I34" t="n" s="0">
+        <v>190.9987</v>
+      </c>
+      <c r="J34" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B35" t="s" s="0">
+        <v>113</v>
+      </c>
+      <c r="C35" t="s" s="0">
+        <v>114</v>
+      </c>
+      <c r="D35" t="s" s="0">
+        <v>115</v>
+      </c>
+      <c r="E35" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F35" t="n" s="0">
+        <v>19.7619</v>
+      </c>
+      <c r="G35" t="n" s="0">
+        <v>19.7619</v>
+      </c>
+      <c r="H35" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="I35" t="n" s="0">
+        <v>19.7619</v>
+      </c>
+      <c r="J35" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B36" t="s" s="0">
+        <v>116</v>
+      </c>
+      <c r="C36" t="s" s="0">
+        <v>117</v>
+      </c>
+      <c r="D36" t="s" s="0">
+        <v>118</v>
+      </c>
+      <c r="E36" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F36" t="n" s="0">
+        <v>19.5837</v>
+      </c>
+      <c r="G36" t="n" s="0">
+        <v>19.5837</v>
+      </c>
+      <c r="H36" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="I36" t="n" s="0">
+        <v>19.5837</v>
+      </c>
+      <c r="J36" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B37" t="s" s="0">
+        <v>119</v>
+      </c>
+      <c r="C37" t="s" s="0">
+        <v>120</v>
+      </c>
+      <c r="D37" t="s" s="0">
+        <v>121</v>
+      </c>
+      <c r="E37" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F37" t="n" s="0">
+        <v>16.0663</v>
+      </c>
+      <c r="G37" t="n" s="0">
+        <v>16.0663</v>
+      </c>
+      <c r="H37" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="I37" t="n" s="0">
+        <v>16.0663</v>
+      </c>
+      <c r="J37" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B38" t="s" s="0">
+        <v>122</v>
+      </c>
+      <c r="C38" t="s" s="0">
+        <v>123</v>
+      </c>
+      <c r="D38" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="E38" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F38" t="n" s="0">
+        <v>99.8315</v>
+      </c>
+      <c r="G38" t="n" s="0">
+        <v>99.8315</v>
+      </c>
+      <c r="H38" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="I38" t="n" s="0">
+        <v>99.8315</v>
+      </c>
+      <c r="J38" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B39" t="s" s="0">
+        <v>125</v>
+      </c>
+      <c r="C39" t="s" s="0">
+        <v>126</v>
+      </c>
+      <c r="D39" t="s" s="0">
+        <v>127</v>
+      </c>
+      <c r="E39" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F39" t="n" s="0">
+        <v>56.8281</v>
+      </c>
+      <c r="G39" t="n" s="0">
+        <v>56.8281</v>
+      </c>
+      <c r="H39" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="I39" t="n" s="0">
+        <v>56.8281</v>
+      </c>
+      <c r="J39" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B40" t="s" s="0">
+        <v>128</v>
+      </c>
+      <c r="C40" t="s" s="0">
+        <v>129</v>
+      </c>
+      <c r="D40" t="s" s="0">
+        <v>130</v>
+      </c>
+      <c r="E40" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="F40" t="n" s="0">
+        <v>78.8649</v>
+      </c>
+      <c r="G40" t="n" s="0">
+        <v>7.88649</v>
+      </c>
+      <c r="H40" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="I40" t="n" s="0">
+        <v>7.88649</v>
+      </c>
+      <c r="J40" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B41" t="s" s="0">
+        <v>131</v>
+      </c>
+      <c r="C41" t="s" s="0">
+        <v>132</v>
+      </c>
+      <c r="D41" t="s" s="0">
+        <v>133</v>
+      </c>
+      <c r="E41" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="F41" t="n" s="0">
+        <v>22.3484</v>
+      </c>
+      <c r="G41" t="n" s="0">
+        <v>2.23484</v>
+      </c>
+      <c r="H41" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="I41" t="n" s="0">
+        <v>2.23484</v>
+      </c>
+      <c r="J41" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B42" t="s" s="0">
+        <v>134</v>
+      </c>
+      <c r="C42" t="s" s="0">
+        <v>135</v>
+      </c>
+      <c r="D42" t="s" s="0">
+        <v>136</v>
+      </c>
+      <c r="E42" t="n" s="0">
+        <v>100.0</v>
+      </c>
+      <c r="F42" t="n" s="0">
+        <v>59.7554</v>
+      </c>
+      <c r="G42" t="n" s="0">
+        <v>0.597554</v>
+      </c>
+      <c r="H42" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="I42" t="n" s="0">
+        <v>0.597554</v>
+      </c>
+      <c r="J42" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B43" t="s" s="0">
+        <v>137</v>
+      </c>
+      <c r="C43" t="s" s="0">
+        <v>138</v>
+      </c>
+      <c r="D43" t="s" s="0">
+        <v>139</v>
+      </c>
+      <c r="E43" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="F43" t="n" s="0">
+        <v>15.8658</v>
+      </c>
+      <c r="G43" t="n" s="0">
+        <v>1.58658</v>
+      </c>
+      <c r="H43" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="I43" t="n" s="0">
+        <v>1.58658</v>
+      </c>
+      <c r="J43" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B44" t="s" s="0">
+        <v>140</v>
+      </c>
+      <c r="C44" t="s" s="0">
+        <v>141</v>
+      </c>
+      <c r="D44" t="s" s="0">
+        <v>142</v>
+      </c>
+      <c r="E44" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F44" t="n" s="0">
+        <v>20.9826</v>
+      </c>
+      <c r="G44" t="n" s="0">
+        <v>20.9826</v>
+      </c>
+      <c r="H44" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="I44" t="n" s="0">
+        <v>20.9826</v>
+      </c>
+      <c r="J44" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B45" t="s" s="0">
+        <v>143</v>
+      </c>
+      <c r="C45" t="s" s="0">
+        <v>144</v>
+      </c>
+      <c r="D45" t="s" s="0">
+        <v>145</v>
+      </c>
+      <c r="E45" t="n" s="0">
+        <v>10000.0</v>
+      </c>
+      <c r="F45" t="n" s="0">
+        <v>60.9025</v>
+      </c>
+      <c r="G45" t="n" s="0">
+        <v>0.00609025</v>
+      </c>
+      <c r="H45" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="I45" t="n" s="0">
+        <v>0.00609025</v>
+      </c>
+      <c r="J45" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B46" t="s" s="0">
+        <v>146</v>
+      </c>
+      <c r="C46" t="s" s="0">
+        <v>147</v>
+      </c>
+      <c r="D46" t="s" s="0">
+        <v>148</v>
+      </c>
+      <c r="E46" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="F46" t="n" s="0">
+        <v>16.3537</v>
+      </c>
+      <c r="G46" t="n" s="0">
+        <v>1.63537</v>
+      </c>
+      <c r="H46" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="I46" t="n" s="0">
+        <v>1.63537</v>
+      </c>
+      <c r="J46" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B47" t="s" s="0">
+        <v>149</v>
+      </c>
+      <c r="C47" t="s" s="0">
+        <v>150</v>
+      </c>
+      <c r="D47" t="s" s="0">
+        <v>151</v>
+      </c>
+      <c r="E47" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="F47" t="n" s="0">
+        <v>34.7624</v>
+      </c>
+      <c r="G47" t="n" s="0">
+        <v>3.4762399999999998</v>
+      </c>
+      <c r="H47" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="I47" t="n" s="0">
+        <v>3.4762399999999998</v>
+      </c>
+      <c r="J47" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B48" t="s" s="0">
+        <v>152</v>
+      </c>
+      <c r="C48" t="s" s="0">
+        <v>153</v>
+      </c>
+      <c r="D48" t="s" s="0">
+        <v>154</v>
+      </c>
+      <c r="E48" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="F48" t="n" s="0">
+        <v>76.6248</v>
+      </c>
+      <c r="G48" t="n" s="0">
+        <v>7.6624799999999995</v>
+      </c>
+      <c r="H48" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="I48" t="n" s="0">
+        <v>7.6624799999999995</v>
+      </c>
+      <c r="J48" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B49" t="s" s="0">
+        <v>155</v>
+      </c>
+      <c r="C49" t="s" s="0">
+        <v>156</v>
+      </c>
+      <c r="D49" t="s" s="0">
+        <v>157</v>
+      </c>
+      <c r="E49" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F49" t="n" s="0">
+        <v>91.1267</v>
+      </c>
+      <c r="G49" t="n" s="0">
+        <v>91.1267</v>
+      </c>
+      <c r="H49" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="I49" t="n" s="0">
+        <v>91.1267</v>
+      </c>
+      <c r="J49" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B50" t="s" s="0">
+        <v>158</v>
+      </c>
+      <c r="C50" t="s" s="0">
+        <v>159</v>
+      </c>
+      <c r="D50" t="s" s="0">
+        <v>160</v>
+      </c>
+      <c r="E50" t="n" s="0">
+        <v>100.0</v>
+      </c>
+      <c r="F50" t="n" s="0">
+        <v>46.2233</v>
+      </c>
+      <c r="G50" t="n" s="0">
+        <v>0.462233</v>
+      </c>
+      <c r="H50" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="I50" t="n" s="0">
+        <v>0.462233</v>
+      </c>
+      <c r="J50" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B51" t="s" s="0">
+        <v>161</v>
+      </c>
+      <c r="C51" t="s" s="0">
+        <v>162</v>
+      </c>
+      <c r="D51" t="s" s="0">
+        <v>163</v>
+      </c>
+      <c r="E51" t="n" s="0">
+        <v>100.0</v>
+      </c>
+      <c r="F51" t="n" s="0">
+        <v>71.4752</v>
+      </c>
+      <c r="G51" t="n" s="0">
+        <v>0.714752</v>
+      </c>
+      <c r="H51" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="I51" t="n" s="0">
+        <v>0.714752</v>
+      </c>
+      <c r="J51" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B52" t="s" s="0">
+        <v>164</v>
+      </c>
+      <c r="C52" t="s" s="0">
+        <v>165</v>
+      </c>
+      <c r="D52" t="s" s="0">
+        <v>166</v>
+      </c>
+      <c r="E52" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="F52" t="n" s="0">
+        <v>44.5693</v>
+      </c>
+      <c r="G52" t="n" s="0">
+        <v>4.45693</v>
+      </c>
+      <c r="H52" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="I52" t="n" s="0">
+        <v>4.45693</v>
+      </c>
+      <c r="J52" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B53" t="s" s="0">
+        <v>167</v>
+      </c>
+      <c r="C53" t="s" s="0">
+        <v>168</v>
+      </c>
+      <c r="D53" t="s" s="0">
+        <v>169</v>
+      </c>
+      <c r="E53" t="n" s="0">
+        <v>1000.0</v>
+      </c>
+      <c r="F53" t="n" s="0">
+        <v>48.2073</v>
+      </c>
+      <c r="G53" t="n" s="0">
+        <v>0.048207299999999995</v>
+      </c>
+      <c r="H53" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="I53" t="n" s="0">
+        <v>0.048207299999999995</v>
+      </c>
+      <c r="J53" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B54" t="s" s="0">
+        <v>170</v>
+      </c>
+      <c r="C54" t="s" s="0">
+        <v>171</v>
+      </c>
+      <c r="D54" t="s" s="0">
+        <v>172</v>
+      </c>
+      <c r="E54" t="n" s="0">
+        <v>100.0</v>
+      </c>
+      <c r="F54" t="n" s="0">
+        <v>45.5775</v>
+      </c>
+      <c r="G54" t="n" s="0">
+        <v>0.455775</v>
+      </c>
+      <c r="H54" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="I54" t="n" s="0">
+        <v>0.455775</v>
+      </c>
+      <c r="J54" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B55" t="s" s="0">
+        <v>173</v>
+      </c>
+      <c r="C55" t="s" s="0">
+        <v>174</v>
+      </c>
+      <c r="D55" t="s" s="0">
+        <v>175</v>
+      </c>
+      <c r="E55" t="n" s="0">
+        <v>1000.0</v>
+      </c>
+      <c r="F55" t="n" s="0">
+        <v>34.971</v>
+      </c>
+      <c r="G55" t="n" s="0">
+        <v>0.034970999999999995</v>
+      </c>
+      <c r="H55" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="I55" t="n" s="0">
+        <v>0.034970999999999995</v>
+      </c>
+      <c r="J55" t="s" s="0">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
